--- a/Synthetic_data/OUTPUT2_frozen/data_leaf_damage_singlemetrics.xlsx
+++ b/Synthetic_data/OUTPUT2_frozen/data_leaf_damage_singlemetrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,55 +449,60 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>total_interisland_distances</t>
+          <t>total_nearest_island_distances</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>mean_nearest_island_distance</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>island_counts</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>total_leaf_size_px</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>total_leaf_size_cm2</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>total_damage_area_px</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_damage_area_cm2</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_damage_percentage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>threshold_val_leaf</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>threshold_val_dmg</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>background_leaf</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>background_dmg</t>
         </is>
@@ -535,24 +540,27 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>69046</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -583,29 +591,32 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
         <v>69046</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
         <v>17326</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
         <v>25.0934159835472</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
       <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>2</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -638,29 +649,32 @@
         <v>531.7821573140218</v>
       </c>
       <c r="H4" t="n">
+        <v>14.37249073821681</v>
+      </c>
+      <c r="I4" t="n">
         <v>37</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>69046</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
         <v>18093</v>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
         <v>26.20426961735654</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>2</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -693,29 +707,32 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
         <v>69046</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
         <v>18414</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
         <v>26.66917707035889</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -748,29 +765,32 @@
         <v>206</v>
       </c>
       <c r="H6" t="n">
+        <v>103</v>
+      </c>
+      <c r="I6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>69046</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
         <v>8842</v>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
         <v>12.80595544998986</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
       <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Synthetic_data/OUTPUT2_frozen/data_leaf_damage_singlemetrics.xlsx
+++ b/Synthetic_data/OUTPUT2_frozen/data_leaf_damage_singlemetrics.xlsx
@@ -659,11 +659,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>18093</v>
+        <v>18075</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>26.20426961735654</v>
+        <v>26.17820004055267</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -717,11 +717,11 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>18414</v>
+        <v>16341</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>26.66917707035889</v>
+        <v>23.66683080844654</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
